--- a/Project_Up/dailyTop.xlsx
+++ b/Project_Up/dailyTop.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="2026-09-04" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="2026-09-07" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -773,4 +774,334 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Stock</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Change %</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>ALKALI</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>PKTEA</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>MVGJL</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>PCJEWELLER</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>18.3</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>TEXMOPIPES</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>17.67</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>CENTUM</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>14.46</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>RADHIKAJWE</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>14.29</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>SYRMA</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="n">
+        <v>12.26</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>RUBYMILLS</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>11.86</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>ANDHRAPAP</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n">
+        <v>11.09</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>STAR</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>11.08</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>THEMISMED</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="n">
+        <v>10.95</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>ORIENTPPR</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>10.66</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>ANUHPHR</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n">
+        <v>10.6</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>MGEL</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>10.39</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>BODALCHEM</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>FCL</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>TBZ</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="n">
+        <v>9.99</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>VENUSPIPES</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>9.94</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>SIGNPOST</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="n">
+        <v>9.789999999999999</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>CHEMPLASTS</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>9.640000000000001</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>ARFIN</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="n">
+        <v>9.640000000000001</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>KABRAEXTRU</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="n">
+        <v>9.56</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>SOLARA</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="n">
+        <v>9.49</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>QUICKHEAL</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="n">
+        <v>9.27</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>RISHABH</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="n">
+        <v>9.26</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>MMP</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="n">
+        <v>9.119999999999999</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>AVONMORE</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="n">
+        <v>9.06</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>BBOX</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="n">
+        <v>8.699999999999999</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>MOTOGENFIN</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="n">
+        <v>8.5</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/Project_Up/dailyTop.xlsx
+++ b/Project_Up/dailyTop.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet name="2026-09-04" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="2026-09-07" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="2026-09-08" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1104,4 +1105,334 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Stock</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Change %</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>ALKALI</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>33.23</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>PKTEA</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>23.47</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>PODDARMENT</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>22.71</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>MMP</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>18.46</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>GENESYS</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>17.43</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>BAIDFIN</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>17.09</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>VENUSPIPES</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>16.68</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>ASTEC</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="n">
+        <v>15.96</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>RAYMOND</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>15.62</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>MVGJL</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n">
+        <v>15.59</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>TBZ</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>15.48</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>BODALCHEM</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="n">
+        <v>13.54</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>SYRMA</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>13.5</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>MIDHANI</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n">
+        <v>13.24</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>CORDSCABLE</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>12.67</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>KOTHARIPET</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="n">
+        <v>12.63</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>SAKAR</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>12.44</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>CHEMBOND</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="n">
+        <v>11.7</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>AIRAN</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>11.53</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>RAYMONDREL</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="n">
+        <v>11.18</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>GMMPFAUDLR</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>10.94</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>WHEELS</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="n">
+        <v>10.8</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>RISHABH</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="n">
+        <v>10.42</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>SPECTRUM</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="n">
+        <v>10.25</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>MBECL</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="n">
+        <v>10.25</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>SYSTMTXC</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="n">
+        <v>10.24</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>STLTECH</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="n">
+        <v>10.24</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>STLNETWORK</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="n">
+        <v>10.22</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>BHAGERIA</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="n">
+        <v>10.22</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>INDIAGLYCO</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="n">
+        <v>10.22</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>